--- a/data/processed/y_train.xlsx
+++ b/data/processed/y_train.xlsx
@@ -430,7 +430,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -445,7 +445,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -455,7 +455,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -475,12 +475,12 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -490,12 +490,12 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -510,7 +510,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -520,7 +520,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -540,22 +540,22 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -570,7 +570,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -580,7 +580,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -590,37 +590,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -640,17 +640,17 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -665,7 +665,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -675,12 +675,12 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -735,12 +735,12 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -755,7 +755,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -785,17 +785,17 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -805,7 +805,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -820,7 +820,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -845,7 +845,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -855,22 +855,22 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -880,17 +880,17 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -915,7 +915,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -925,7 +925,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -940,7 +940,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -960,12 +960,12 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -985,7 +985,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -1000,7 +1000,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -1015,17 +1015,17 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -1035,22 +1035,22 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -1060,7 +1060,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -1085,12 +1085,12 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -1105,7 +1105,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -1115,7 +1115,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -1145,12 +1145,12 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -1180,12 +1180,12 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -1225,7 +1225,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -1255,12 +1255,12 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -1270,7 +1270,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -1280,12 +1280,12 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -1300,12 +1300,12 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -1320,12 +1320,12 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -1335,12 +1335,12 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -1350,17 +1350,17 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -1370,7 +1370,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -1380,7 +1380,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -1390,7 +1390,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -1410,22 +1410,22 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -1445,17 +1445,17 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -1490,7 +1490,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -1500,12 +1500,12 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -1515,12 +1515,12 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -1540,37 +1540,37 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -1620,7 +1620,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -1630,7 +1630,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -1660,22 +1660,22 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -1705,7 +1705,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -1715,22 +1715,22 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -1745,17 +1745,17 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -1770,12 +1770,12 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -1790,12 +1790,12 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -1840,12 +1840,12 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -1865,17 +1865,17 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -1890,17 +1890,17 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -1910,12 +1910,12 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -1930,12 +1930,12 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -1960,12 +1960,12 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -1990,7 +1990,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -2000,12 +2000,12 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -2015,17 +2015,17 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -2060,7 +2060,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -2085,7 +2085,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -2110,7 +2110,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -2145,7 +2145,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -2160,7 +2160,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -2170,12 +2170,12 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -2185,7 +2185,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -2195,12 +2195,12 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -2235,27 +2235,27 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
@@ -2270,7 +2270,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
@@ -2280,17 +2280,17 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -2320,12 +2320,12 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -2340,17 +2340,17 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
@@ -2360,7 +2360,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -2370,17 +2370,17 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -2390,7 +2390,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396">
@@ -2410,7 +2410,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400">
@@ -2425,7 +2425,7 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
@@ -2440,7 +2440,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406">
@@ -2450,7 +2450,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -2460,17 +2460,17 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -2485,7 +2485,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
@@ -2500,7 +2500,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
@@ -2510,7 +2510,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -2520,7 +2520,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422">
@@ -2540,12 +2540,12 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -2555,7 +2555,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -2570,7 +2570,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -2580,12 +2580,12 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -2600,7 +2600,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -2615,17 +2615,17 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -2635,12 +2635,12 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -2660,32 +2660,32 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -2710,12 +2710,12 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -2735,7 +2735,7 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -2745,12 +2745,12 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -2765,7 +2765,7 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -2790,17 +2790,17 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -2835,12 +2835,12 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486">
@@ -2850,12 +2850,12 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489">
@@ -2865,7 +2865,7 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491">
@@ -2885,17 +2885,17 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -2905,7 +2905,7 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -2915,12 +2915,12 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502">
@@ -2930,7 +2930,7 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -2945,17 +2945,17 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="509">
@@ -2970,7 +2970,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -2980,17 +2980,17 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516">
@@ -3010,17 +3010,17 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -3030,7 +3030,7 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -3040,12 +3040,12 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
@@ -3055,12 +3055,12 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -3075,7 +3075,7 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -3085,7 +3085,7 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
@@ -3100,17 +3100,17 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540">
@@ -3125,17 +3125,17 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -3145,7 +3145,7 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -3160,7 +3160,7 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550">
@@ -3180,17 +3180,17 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
@@ -3205,7 +3205,7 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
@@ -3225,7 +3225,7 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563">
@@ -3235,7 +3235,7 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
@@ -3255,12 +3255,12 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570">
@@ -3270,37 +3270,37 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="578">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="582">
@@ -3335,12 +3335,12 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="586">
@@ -3365,12 +3365,12 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="592">
@@ -3395,17 +3395,17 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="599">
@@ -3415,32 +3415,32 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606">
@@ -3450,12 +3450,12 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="609">
@@ -3470,7 +3470,7 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612">
@@ -3485,7 +3485,7 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
